--- a/artfynd/A 15298-2025 artfynd.xlsx
+++ b/artfynd/A 15298-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123996515</v>
+        <v>123997146</v>
       </c>
       <c r="B2" t="n">
         <v>98079</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578557</v>
+        <v>578567</v>
       </c>
       <c r="R2" t="n">
-        <v>7022352</v>
+        <v>7022229</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123997146</v>
+        <v>123996407</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578567</v>
+        <v>578575</v>
       </c>
       <c r="R3" t="n">
-        <v>7022229</v>
+        <v>7022344</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123996170</v>
+        <v>123996081</v>
       </c>
       <c r="B4" t="n">
-        <v>96957</v>
+        <v>90990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578575</v>
+        <v>578546</v>
       </c>
       <c r="R4" t="n">
-        <v>7022278</v>
+        <v>7022265</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123996407</v>
+        <v>123996170</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>96957</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,32 +1001,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmon, Långmon, Ång</t>
@@ -1036,7 +1032,7 @@
         <v>578575</v>
       </c>
       <c r="R5" t="n">
-        <v>7022344</v>
+        <v>7022278</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1095,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123996081</v>
+        <v>123996515</v>
       </c>
       <c r="B6" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1107,38 +1103,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långmon, Långmon, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578546</v>
+        <v>578557</v>
       </c>
       <c r="R6" t="n">
-        <v>7022265</v>
+        <v>7022352</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 15298-2025 artfynd.xlsx
+++ b/artfynd/A 15298-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123997146</v>
+        <v>123996081</v>
       </c>
       <c r="B2" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmon, Långmon, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578567</v>
+        <v>578546</v>
       </c>
       <c r="R2" t="n">
-        <v>7022229</v>
+        <v>7022265</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -781,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123996407</v>
+        <v>123996515</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -825,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578575</v>
+        <v>578557</v>
       </c>
       <c r="R3" t="n">
-        <v>7022344</v>
+        <v>7022352</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -887,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123996081</v>
+        <v>123996170</v>
       </c>
       <c r="B4" t="n">
-        <v>90990</v>
+        <v>96957</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +895,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578546</v>
+        <v>578575</v>
       </c>
       <c r="R4" t="n">
-        <v>7022265</v>
+        <v>7022278</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -989,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123996170</v>
+        <v>123997146</v>
       </c>
       <c r="B5" t="n">
-        <v>96957</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,38 +997,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmon, Långmon, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578575</v>
+        <v>578567</v>
       </c>
       <c r="R5" t="n">
-        <v>7022278</v>
+        <v>7022229</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1091,7 +1091,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123996515</v>
+        <v>123996407</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578557</v>
+        <v>578575</v>
       </c>
       <c r="R6" t="n">
-        <v>7022352</v>
+        <v>7022344</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 15298-2025 artfynd.xlsx
+++ b/artfynd/A 15298-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123996170</v>
+        <v>123996515</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmon, Långmon, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578575</v>
+        <v>578557</v>
       </c>
       <c r="R2" t="n">
-        <v>7022278</v>
+        <v>7022352</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123996081</v>
+        <v>123996170</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>96979</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578546</v>
+        <v>578575</v>
       </c>
       <c r="R3" t="n">
-        <v>7022265</v>
+        <v>7022278</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,7 +883,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123997146</v>
+        <v>123996407</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -914,7 +918,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -923,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578567</v>
+        <v>578575</v>
       </c>
       <c r="R4" t="n">
-        <v>7022229</v>
+        <v>7022344</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,7 +989,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123996407</v>
+        <v>123997146</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1020,7 +1024,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1029,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578575</v>
+        <v>578567</v>
       </c>
       <c r="R5" t="n">
-        <v>7022344</v>
+        <v>7022229</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1091,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123996515</v>
+        <v>123996081</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,42 +1107,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långmon, Långmon, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578557</v>
+        <v>578546</v>
       </c>
       <c r="R6" t="n">
-        <v>7022352</v>
+        <v>7022265</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 15298-2025 artfynd.xlsx
+++ b/artfynd/A 15298-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123996515</v>
+        <v>123996407</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578557</v>
+        <v>578575</v>
       </c>
       <c r="R2" t="n">
-        <v>7022352</v>
+        <v>7022344</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123996170</v>
+        <v>123997146</v>
       </c>
       <c r="B3" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmon, Långmon, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578575</v>
+        <v>578567</v>
       </c>
       <c r="R3" t="n">
-        <v>7022278</v>
+        <v>7022229</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -883,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123996407</v>
+        <v>123996515</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -927,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578575</v>
+        <v>578557</v>
       </c>
       <c r="R4" t="n">
-        <v>7022344</v>
+        <v>7022352</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -989,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123997146</v>
+        <v>123996170</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,42 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmon, Långmon, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578567</v>
+        <v>578575</v>
       </c>
       <c r="R5" t="n">
-        <v>7022229</v>
+        <v>7022278</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 15298-2025 artfynd.xlsx
+++ b/artfynd/A 15298-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123996407</v>
+        <v>123996515</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578575</v>
+        <v>578557</v>
       </c>
       <c r="R2" t="n">
-        <v>7022344</v>
+        <v>7022352</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123997146</v>
+        <v>123996081</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,42 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmon, Långmon, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578567</v>
+        <v>578546</v>
       </c>
       <c r="R3" t="n">
-        <v>7022229</v>
+        <v>7022265</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -887,7 +883,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123996515</v>
+        <v>123996407</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -931,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578557</v>
+        <v>578575</v>
       </c>
       <c r="R4" t="n">
-        <v>7022352</v>
+        <v>7022344</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -993,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123996170</v>
+        <v>123997146</v>
       </c>
       <c r="B5" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1001,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmon, Långmon, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578575</v>
+        <v>578567</v>
       </c>
       <c r="R5" t="n">
-        <v>7022278</v>
+        <v>7022229</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123996081</v>
+        <v>123996170</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>96979</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1107,25 +1107,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578546</v>
+        <v>578575</v>
       </c>
       <c r="R6" t="n">
-        <v>7022265</v>
+        <v>7022278</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 15298-2025 artfynd.xlsx
+++ b/artfynd/A 15298-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123996515</v>
+        <v>123996407</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578557</v>
+        <v>578575</v>
       </c>
       <c r="R2" t="n">
-        <v>7022352</v>
+        <v>7022344</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123996081</v>
+        <v>123997146</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmon, Långmon, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578546</v>
+        <v>578567</v>
       </c>
       <c r="R3" t="n">
-        <v>7022265</v>
+        <v>7022229</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -883,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123996407</v>
+        <v>123996170</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,32 +899,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmon, Långmon, Ång</t>
@@ -930,7 +930,7 @@
         <v>578575</v>
       </c>
       <c r="R4" t="n">
-        <v>7022344</v>
+        <v>7022278</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -989,7 +989,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123997146</v>
+        <v>123996515</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578567</v>
+        <v>578557</v>
       </c>
       <c r="R5" t="n">
-        <v>7022229</v>
+        <v>7022352</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123996170</v>
+        <v>123996081</v>
       </c>
       <c r="B6" t="n">
-        <v>96979</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1107,25 +1107,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578575</v>
+        <v>578546</v>
       </c>
       <c r="R6" t="n">
-        <v>7022278</v>
+        <v>7022265</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 15298-2025 artfynd.xlsx
+++ b/artfynd/A 15298-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123997146</v>
+        <v>123996170</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,42 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmon, Långmon, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578567</v>
+        <v>578575</v>
       </c>
       <c r="R3" t="n">
-        <v>7022229</v>
+        <v>7022278</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -887,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123996170</v>
+        <v>123997146</v>
       </c>
       <c r="B4" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +895,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmon, Långmon, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578575</v>
+        <v>578567</v>
       </c>
       <c r="R4" t="n">
-        <v>7022278</v>
+        <v>7022229</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
